--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136442750</v>
       </c>
       <c r="B4" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136442752</v>
       </c>
       <c r="B5" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136442759</v>
       </c>
       <c r="B6" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136442747</v>
       </c>
       <c r="B7" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136442743</v>
       </c>
       <c r="B8" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136442739</v>
       </c>
       <c r="B9" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>136442744</v>
       </c>
       <c r="B10" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>136442751</v>
       </c>
       <c r="B11" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136442755</v>
       </c>
       <c r="B12" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136442760</v>
       </c>
       <c r="B13" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136442740</v>
       </c>
       <c r="B14" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136442754</v>
       </c>
       <c r="B15" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>136442748</v>
       </c>
       <c r="B16" t="n">
-        <v>96677</v>
+        <v>96680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>136442753</v>
       </c>
       <c r="B17" t="n">
-        <v>96677</v>
+        <v>96680</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136442746</v>
       </c>
       <c r="B21" t="n">
-        <v>92327</v>
+        <v>92330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136442745</v>
       </c>
       <c r="B23" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136442750</v>
       </c>
       <c r="B4" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136442752</v>
       </c>
       <c r="B5" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136442759</v>
       </c>
       <c r="B6" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136442747</v>
       </c>
       <c r="B7" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136442743</v>
       </c>
       <c r="B8" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136442739</v>
       </c>
       <c r="B9" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>136442744</v>
       </c>
       <c r="B10" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>136442751</v>
       </c>
       <c r="B11" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136442755</v>
       </c>
       <c r="B12" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136442760</v>
       </c>
       <c r="B13" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136442740</v>
       </c>
       <c r="B14" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136442754</v>
       </c>
       <c r="B15" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>136442748</v>
       </c>
       <c r="B16" t="n">
-        <v>96680</v>
+        <v>96681</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>136442753</v>
       </c>
       <c r="B17" t="n">
-        <v>96680</v>
+        <v>96681</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136442746</v>
       </c>
       <c r="B21" t="n">
-        <v>92330</v>
+        <v>92331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136442745</v>
       </c>
       <c r="B23" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136442750</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136442752</v>
       </c>
       <c r="B5" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136442759</v>
       </c>
       <c r="B6" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136442747</v>
       </c>
       <c r="B7" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136442743</v>
       </c>
       <c r="B8" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136442739</v>
       </c>
       <c r="B9" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>136442744</v>
       </c>
       <c r="B10" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>136442751</v>
       </c>
       <c r="B11" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136442755</v>
       </c>
       <c r="B12" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136442760</v>
       </c>
       <c r="B13" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136442740</v>
       </c>
       <c r="B14" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136442754</v>
       </c>
       <c r="B15" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>136442748</v>
       </c>
       <c r="B16" t="n">
-        <v>96681</v>
+        <v>96686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>136442753</v>
       </c>
       <c r="B17" t="n">
-        <v>96681</v>
+        <v>96686</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136442746</v>
       </c>
       <c r="B21" t="n">
-        <v>92331</v>
+        <v>92336</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136442745</v>
       </c>
       <c r="B23" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136442750</v>
       </c>
       <c r="B4" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136442752</v>
       </c>
       <c r="B5" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136442759</v>
       </c>
       <c r="B6" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136442747</v>
       </c>
       <c r="B7" t="n">
-        <v>96782</v>
+        <v>96784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136442743</v>
       </c>
       <c r="B8" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136442739</v>
       </c>
       <c r="B9" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>136442744</v>
       </c>
       <c r="B10" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>136442751</v>
       </c>
       <c r="B11" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136442755</v>
       </c>
       <c r="B12" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136442760</v>
       </c>
       <c r="B13" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136442740</v>
       </c>
       <c r="B14" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136442754</v>
       </c>
       <c r="B15" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>136442748</v>
       </c>
       <c r="B16" t="n">
-        <v>96686</v>
+        <v>96688</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>136442753</v>
       </c>
       <c r="B17" t="n">
-        <v>96686</v>
+        <v>96688</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136442746</v>
       </c>
       <c r="B21" t="n">
-        <v>92336</v>
+        <v>92338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136442745</v>
       </c>
       <c r="B23" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136442750</v>
       </c>
       <c r="B4" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136442752</v>
       </c>
       <c r="B5" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136442759</v>
       </c>
       <c r="B6" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136442747</v>
       </c>
       <c r="B7" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136442743</v>
       </c>
       <c r="B8" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136442739</v>
       </c>
       <c r="B9" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>136442744</v>
       </c>
       <c r="B10" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>136442751</v>
       </c>
       <c r="B11" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136442755</v>
       </c>
       <c r="B12" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136442760</v>
       </c>
       <c r="B13" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136442740</v>
       </c>
       <c r="B14" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136442754</v>
       </c>
       <c r="B15" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>136442748</v>
       </c>
       <c r="B16" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>136442753</v>
       </c>
       <c r="B17" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136442746</v>
       </c>
       <c r="B21" t="n">
-        <v>92338</v>
+        <v>92340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136442745</v>
       </c>
       <c r="B23" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136442750</v>
       </c>
       <c r="B4" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136442752</v>
       </c>
       <c r="B5" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136442759</v>
       </c>
       <c r="B6" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136442747</v>
       </c>
       <c r="B7" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136442743</v>
       </c>
       <c r="B8" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136442739</v>
       </c>
       <c r="B9" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>136442744</v>
       </c>
       <c r="B10" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>136442751</v>
       </c>
       <c r="B11" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136442755</v>
       </c>
       <c r="B12" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136442760</v>
       </c>
       <c r="B13" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136442740</v>
       </c>
       <c r="B14" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136442754</v>
       </c>
       <c r="B15" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>136442748</v>
       </c>
       <c r="B16" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>136442753</v>
       </c>
       <c r="B17" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136442746</v>
       </c>
       <c r="B21" t="n">
-        <v>92340</v>
+        <v>92342</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136442745</v>
       </c>
       <c r="B23" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 43278-2025 artfynd.xlsx
+++ b/artfynd/A 43278-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136442750</v>
       </c>
       <c r="B4" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136442752</v>
       </c>
       <c r="B5" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136442759</v>
       </c>
       <c r="B6" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136442747</v>
       </c>
       <c r="B7" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136442743</v>
       </c>
       <c r="B8" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136442739</v>
       </c>
       <c r="B9" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>136442744</v>
       </c>
       <c r="B10" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>136442751</v>
       </c>
       <c r="B11" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136442755</v>
       </c>
       <c r="B12" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136442760</v>
       </c>
       <c r="B13" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>136442740</v>
       </c>
       <c r="B14" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>136442754</v>
       </c>
       <c r="B15" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>136442748</v>
       </c>
       <c r="B16" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>136442753</v>
       </c>
       <c r="B17" t="n">
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>136442746</v>
       </c>
       <c r="B21" t="n">
-        <v>92342</v>
+        <v>92343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>136442745</v>
       </c>
       <c r="B23" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
